--- a/examples/demo/simple_demo.xlsx
+++ b/examples/demo/simple_demo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="tr0001" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="85">
   <si>
     <t xml:space="preserve">tr_uuid:</t>
   </si>
@@ -269,6 +269,9 @@
     <t xml:space="preserve">--headless</t>
   </si>
   <si>
+    <t xml:space="preserve">delay,5</t>
+  </si>
+  <si>
     <t xml:space="preserve">firefox</t>
   </si>
   <si>
@@ -276,6 +279,9 @@
   </si>
   <si>
     <t xml:space="preserve">explicit_wait,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delayMax,1</t>
   </si>
 </sst>
 </file>
@@ -629,7 +635,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultColWidth="11.71484375" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.71484375" defaultRowHeight="12" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -652,10 +658,10 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -710,7 +716,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="11.71484375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.71484375" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -785,7 +791,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="2" width="11.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="40.71"/>
@@ -1007,7 +1013,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="2" width="11.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="28.57"/>
@@ -1290,7 +1296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.86"/>
@@ -1362,8 +1368,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.42"/>
@@ -1420,6 +1426,11 @@
       </c>
       <c r="D4" s="1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1438,8 +1449,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.86"/>
@@ -1459,7 +1470,7 @@
         <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1478,7 +1489,7 @@
         <v>72</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>74</v>
@@ -1492,7 +1503,12 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1512,7 +1528,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.86"/>
@@ -1532,7 +1548,7 @@
         <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1551,7 +1567,7 @@
         <v>72</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>74</v>
@@ -1563,7 +1579,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/examples/demo/simple_demo.xlsx
+++ b/examples/demo/simple_demo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="tr0001" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,8 +15,7 @@
     <sheet name="chrome001" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="chrome002" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="ffox001" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="android" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="ffox002" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="ffox002" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="85">
   <si>
     <t xml:space="preserve">tr_uuid:</t>
   </si>
@@ -66,7 +65,7 @@
     <t xml:space="preserve">reporters:</t>
   </si>
   <si>
-    <t xml:space="preserve">drivers:</t>
+    <t xml:space="preserve">browsers:</t>
   </si>
   <si>
     <t xml:space="preserve">chrome001</t>
@@ -81,18 +80,12 @@
     <t xml:space="preserve">ffox002</t>
   </si>
   <si>
-    <t xml:space="preserve">android001</t>
-  </si>
-  <si>
     <t xml:space="preserve">tr100102</t>
   </si>
   <si>
     <t xml:space="preserve">Simple Demo 2</t>
   </si>
   <si>
-    <t xml:space="preserve">browsers:</t>
-  </si>
-  <si>
     <t xml:space="preserve">chrome002</t>
   </si>
   <si>
@@ -276,6 +269,9 @@
     <t xml:space="preserve">--headless</t>
   </si>
   <si>
+    <t xml:space="preserve">delay,5</t>
+  </si>
+  <si>
     <t xml:space="preserve">firefox</t>
   </si>
   <si>
@@ -285,25 +281,7 @@
     <t xml:space="preserve">explicit_wait,30</t>
   </si>
   <si>
-    <t xml:space="preserve">mb_uuid:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">platform_name:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">android</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key[,value]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">appium:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">--testing1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">--testing,more</t>
+    <t xml:space="preserve">delayMax,1</t>
   </si>
 </sst>
 </file>
@@ -314,7 +292,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -335,11 +313,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -391,16 +364,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -412,7 +381,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -729,11 +698,7 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
+    <row r="5" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -758,13 +723,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -789,10 +754,10 @@
         <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>14</v>
@@ -804,7 +769,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J4" s="1"/>
     </row>
@@ -828,207 +793,207 @@
   <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="3" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="40.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="4" style="3" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="29.57"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="8" style="3" width="11.57"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="2" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="40.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="4" style="2" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="29.57"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="8" style="2" width="11.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="G3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="G5" s="3"/>
+      <c r="H5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="3" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="D7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="I7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="I7" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="3" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1050,268 +1015,268 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="3" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="28.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="28.42"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="3" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="38.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="8" style="3" width="11.57"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="2" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="28.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="28.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="38.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="8" style="2" width="11.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="I7" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="I12" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="I7" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="G8" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="I12" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="G13" s="3"/>
+      <c r="K13" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="K13" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1342,49 +1307,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1403,7 +1368,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
@@ -1415,52 +1380,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>81</v>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1479,7 +1449,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
@@ -1491,48 +1461,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1552,91 +1527,6 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.42"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1649,47 +1539,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
